--- a/MAC286_3076_Data Structures_Spring2026_Attndance.xlsx
+++ b/MAC286_3076_Data Structures_Spring2026_Attndance.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="17256" windowHeight="5424"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="17280" windowHeight="6912"/>
   </bookViews>
   <sheets>
     <sheet name="Grades" sheetId="1" r:id="rId1"/>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="170" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="198" uniqueCount="34">
   <si>
     <t>Last Name</t>
   </si>
@@ -609,9 +609,10 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="17" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -933,7 +934,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:L15"/>
+  <dimension ref="A1:N15"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="3" max="3" width="9.44140625" bestFit="1" customWidth="1"/>
@@ -941,9 +942,10 @@
     <col min="5" max="9" width="9.44140625" bestFit="1" customWidth="1"/>
     <col min="10" max="11" width="9.6640625" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="9.5546875" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="9.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -980,8 +982,14 @@
       <c r="L1" s="1">
         <v>46140</v>
       </c>
+      <c r="M1" s="1">
+        <v>46142</v>
+      </c>
+      <c r="N1" s="1">
+        <v>46147</v>
+      </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -1018,46 +1026,58 @@
       <c r="L2" t="s">
         <v>31</v>
       </c>
+      <c r="M2" t="s">
+        <v>30</v>
+      </c>
+      <c r="N2" t="s">
+        <v>30</v>
+      </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
+    <row r="3" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C3" t="s">
-        <v>30</v>
-      </c>
-      <c r="D3" t="s">
-        <v>31</v>
-      </c>
-      <c r="E3" t="s">
-        <v>31</v>
-      </c>
-      <c r="F3" t="s">
-        <v>31</v>
-      </c>
-      <c r="G3" t="s">
-        <v>30</v>
-      </c>
-      <c r="H3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I3" t="s">
-        <v>31</v>
-      </c>
-      <c r="J3" t="s">
-        <v>31</v>
-      </c>
-      <c r="K3" t="s">
-        <v>30</v>
-      </c>
-      <c r="L3" t="s">
+      <c r="C3" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="I3" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="J3" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="K3" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="L3" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="M3" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="N3" s="2" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>6</v>
       </c>
@@ -1094,8 +1114,14 @@
       <c r="L4" t="s">
         <v>33</v>
       </c>
+      <c r="M4" t="s">
+        <v>30</v>
+      </c>
+      <c r="N4" t="s">
+        <v>30</v>
+      </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>8</v>
       </c>
@@ -1132,8 +1158,14 @@
       <c r="L5" t="s">
         <v>30</v>
       </c>
+      <c r="M5" t="s">
+        <v>30</v>
+      </c>
+      <c r="N5" t="s">
+        <v>30</v>
+      </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>10</v>
       </c>
@@ -1170,46 +1202,58 @@
       <c r="L6" t="s">
         <v>30</v>
       </c>
+      <c r="M6" t="s">
+        <v>30</v>
+      </c>
+      <c r="N6" t="s">
+        <v>30</v>
+      </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
+    <row r="7" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B7" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="C7" t="s">
-        <v>30</v>
-      </c>
-      <c r="D7" t="s">
-        <v>31</v>
-      </c>
-      <c r="E7" t="s">
-        <v>30</v>
-      </c>
-      <c r="F7" t="s">
-        <v>31</v>
-      </c>
-      <c r="G7" t="s">
-        <v>30</v>
-      </c>
-      <c r="H7" t="s">
-        <v>30</v>
-      </c>
-      <c r="I7" t="s">
-        <v>30</v>
-      </c>
-      <c r="J7" t="s">
-        <v>30</v>
-      </c>
-      <c r="K7" t="s">
-        <v>30</v>
-      </c>
-      <c r="L7" t="s">
-        <v>31</v>
+      <c r="C7" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="H7" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="I7" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="J7" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="K7" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="L7" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="M7" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="N7" s="2" t="s">
+        <v>30</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>14</v>
       </c>
@@ -1246,8 +1290,14 @@
       <c r="L8" t="s">
         <v>30</v>
       </c>
+      <c r="M8" t="s">
+        <v>30</v>
+      </c>
+      <c r="N8" t="s">
+        <v>30</v>
+      </c>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>16</v>
       </c>
@@ -1284,8 +1334,14 @@
       <c r="L9" t="s">
         <v>31</v>
       </c>
+      <c r="M9" t="s">
+        <v>33</v>
+      </c>
+      <c r="N9" t="s">
+        <v>31</v>
+      </c>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>18</v>
       </c>
@@ -1322,46 +1378,58 @@
       <c r="L10" t="s">
         <v>30</v>
       </c>
+      <c r="M10" t="s">
+        <v>30</v>
+      </c>
+      <c r="N10" t="s">
+        <v>30</v>
+      </c>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A11" t="s">
+    <row r="11" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="B11" t="s">
+      <c r="B11" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="C11" t="s">
-        <v>30</v>
-      </c>
-      <c r="D11" t="s">
-        <v>31</v>
-      </c>
-      <c r="E11" t="s">
-        <v>30</v>
-      </c>
-      <c r="F11" t="s">
-        <v>31</v>
-      </c>
-      <c r="G11" t="s">
-        <v>30</v>
-      </c>
-      <c r="H11" t="s">
-        <v>30</v>
-      </c>
-      <c r="I11" t="s">
-        <v>31</v>
-      </c>
-      <c r="J11" t="s">
-        <v>30</v>
-      </c>
-      <c r="K11" t="s">
-        <v>30</v>
-      </c>
-      <c r="L11" t="s">
+      <c r="C11" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="F11" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="G11" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="H11" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="I11" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="J11" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="K11" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="L11" s="2" t="s">
         <v>33</v>
       </c>
+      <c r="M11" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="N11" s="2" t="s">
+        <v>30</v>
+      </c>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>22</v>
       </c>
@@ -1398,8 +1466,14 @@
       <c r="L12" t="s">
         <v>30</v>
       </c>
+      <c r="M12" t="s">
+        <v>30</v>
+      </c>
+      <c r="N12" t="s">
+        <v>30</v>
+      </c>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>24</v>
       </c>
@@ -1436,46 +1510,58 @@
       <c r="L13" t="s">
         <v>33</v>
       </c>
+      <c r="M13" t="s">
+        <v>30</v>
+      </c>
+      <c r="N13" t="s">
+        <v>30</v>
+      </c>
     </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A14" t="s">
+    <row r="14" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="B14" t="s">
+      <c r="B14" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="C14" t="s">
-        <v>30</v>
-      </c>
-      <c r="D14" t="s">
-        <v>30</v>
-      </c>
-      <c r="E14" t="s">
-        <v>30</v>
-      </c>
-      <c r="F14" t="s">
-        <v>31</v>
-      </c>
-      <c r="G14" t="s">
-        <v>30</v>
-      </c>
-      <c r="H14" t="s">
-        <v>30</v>
-      </c>
-      <c r="I14" t="s">
-        <v>31</v>
-      </c>
-      <c r="J14" t="s">
-        <v>30</v>
-      </c>
-      <c r="K14" t="s">
-        <v>30</v>
-      </c>
-      <c r="L14" t="s">
-        <v>31</v>
+      <c r="C14" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="F14" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="G14" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="H14" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="I14" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="J14" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="K14" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="L14" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="M14" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="N14" s="2" t="s">
+        <v>30</v>
       </c>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>28</v>
       </c>
@@ -1510,10 +1596,17 @@
         <v>30</v>
       </c>
       <c r="L15" t="s">
+        <v>30</v>
+      </c>
+      <c r="M15" t="s">
+        <v>30</v>
+      </c>
+      <c r="N15" t="s">
         <v>30</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967294" verticalDpi="4294967294" r:id="rId1"/>
 </worksheet>
 </file>
--- a/MAC286_3076_Data Structures_Spring2026_Attndance.xlsx
+++ b/MAC286_3076_Data Structures_Spring2026_Attndance.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="198" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="226" uniqueCount="34">
   <si>
     <t>Last Name</t>
   </si>
@@ -934,18 +934,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:N15"/>
+  <dimension ref="A1:P15"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="3" max="3" width="9.44140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.6640625" bestFit="1" customWidth="1"/>
-    <col min="5" max="9" width="9.44140625" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="9.6640625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="9.5546875" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="9.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="14" width="3.5546875" customWidth="1"/>
+    <col min="16" max="16" width="9.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -988,8 +984,14 @@
       <c r="N1" s="1">
         <v>46147</v>
       </c>
+      <c r="O1" s="1">
+        <v>46149</v>
+      </c>
+      <c r="P1" s="1">
+        <v>46154</v>
+      </c>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -1032,8 +1034,14 @@
       <c r="N2" t="s">
         <v>30</v>
       </c>
+      <c r="O2" t="s">
+        <v>30</v>
+      </c>
+      <c r="P2" t="s">
+        <v>31</v>
+      </c>
     </row>
-    <row r="3" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
         <v>4</v>
       </c>
@@ -1076,8 +1084,14 @@
       <c r="N3" s="2" t="s">
         <v>30</v>
       </c>
+      <c r="O3" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="P3" s="2" t="s">
+        <v>30</v>
+      </c>
     </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>6</v>
       </c>
@@ -1120,8 +1134,14 @@
       <c r="N4" t="s">
         <v>30</v>
       </c>
+      <c r="O4" t="s">
+        <v>33</v>
+      </c>
+      <c r="P4" t="s">
+        <v>30</v>
+      </c>
     </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>8</v>
       </c>
@@ -1164,8 +1184,14 @@
       <c r="N5" t="s">
         <v>30</v>
       </c>
+      <c r="O5" t="s">
+        <v>30</v>
+      </c>
+      <c r="P5" t="s">
+        <v>30</v>
+      </c>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>10</v>
       </c>
@@ -1208,8 +1234,14 @@
       <c r="N6" t="s">
         <v>30</v>
       </c>
+      <c r="O6" t="s">
+        <v>30</v>
+      </c>
+      <c r="P6" t="s">
+        <v>30</v>
+      </c>
     </row>
-    <row r="7" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
         <v>12</v>
       </c>
@@ -1252,8 +1284,14 @@
       <c r="N7" s="2" t="s">
         <v>30</v>
       </c>
+      <c r="O7" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="P7" s="2" t="s">
+        <v>31</v>
+      </c>
     </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>14</v>
       </c>
@@ -1296,52 +1334,64 @@
       <c r="N8" t="s">
         <v>30</v>
       </c>
+      <c r="O8" t="s">
+        <v>30</v>
+      </c>
+      <c r="P8" t="s">
+        <v>32</v>
+      </c>
     </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A9" t="s">
+    <row r="9" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="B9" t="s">
+      <c r="B9" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="C9" t="s">
-        <v>30</v>
-      </c>
-      <c r="D9" t="s">
-        <v>30</v>
-      </c>
-      <c r="E9" t="s">
-        <v>30</v>
-      </c>
-      <c r="F9" t="s">
-        <v>30</v>
-      </c>
-      <c r="G9" t="s">
-        <v>31</v>
-      </c>
-      <c r="H9" t="s">
-        <v>30</v>
-      </c>
-      <c r="I9" t="s">
-        <v>30</v>
-      </c>
-      <c r="J9" t="s">
-        <v>30</v>
-      </c>
-      <c r="K9" t="s">
-        <v>30</v>
-      </c>
-      <c r="L9" t="s">
-        <v>31</v>
-      </c>
-      <c r="M9" t="s">
+      <c r="C9" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="G9" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="H9" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="I9" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="J9" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="K9" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="L9" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="M9" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="N9" t="s">
-        <v>31</v>
+      <c r="N9" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="O9" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="P9" s="2" t="s">
+        <v>30</v>
       </c>
     </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>18</v>
       </c>
@@ -1384,8 +1434,14 @@
       <c r="N10" t="s">
         <v>30</v>
       </c>
+      <c r="O10" t="s">
+        <v>30</v>
+      </c>
+      <c r="P10" t="s">
+        <v>30</v>
+      </c>
     </row>
-    <row r="11" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A11" s="2" t="s">
         <v>20</v>
       </c>
@@ -1428,8 +1484,14 @@
       <c r="N11" s="2" t="s">
         <v>30</v>
       </c>
+      <c r="O11" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="P11" s="2" t="s">
+        <v>30</v>
+      </c>
     </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>22</v>
       </c>
@@ -1472,8 +1534,14 @@
       <c r="N12" t="s">
         <v>30</v>
       </c>
+      <c r="O12" t="s">
+        <v>31</v>
+      </c>
+      <c r="P12" t="s">
+        <v>30</v>
+      </c>
     </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>24</v>
       </c>
@@ -1516,8 +1584,14 @@
       <c r="N13" t="s">
         <v>30</v>
       </c>
+      <c r="O13" t="s">
+        <v>30</v>
+      </c>
+      <c r="P13" s="2" t="s">
+        <v>30</v>
+      </c>
     </row>
-    <row r="14" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A14" s="2" t="s">
         <v>26</v>
       </c>
@@ -1560,8 +1634,14 @@
       <c r="N14" s="2" t="s">
         <v>30</v>
       </c>
+      <c r="O14" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="P14" s="2" t="s">
+        <v>30</v>
+      </c>
     </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>28</v>
       </c>
@@ -1602,6 +1682,12 @@
         <v>30</v>
       </c>
       <c r="N15" t="s">
+        <v>30</v>
+      </c>
+      <c r="O15" t="s">
+        <v>30</v>
+      </c>
+      <c r="P15" s="2" t="s">
         <v>30</v>
       </c>
     </row>

--- a/MAC286_3076_Data Structures_Spring2026_Attndance.xlsx
+++ b/MAC286_3076_Data Structures_Spring2026_Attndance.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="226" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="226" uniqueCount="35">
   <si>
     <t>Last Name</t>
   </si>
@@ -126,6 +126,9 @@
   </si>
   <si>
     <t>LATE</t>
+  </si>
+  <si>
+    <t>Late</t>
   </si>
 </sst>
 </file>
@@ -1288,7 +1291,7 @@
         <v>30</v>
       </c>
       <c r="P7" s="2" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
     </row>
     <row r="8" spans="1:16" x14ac:dyDescent="0.3">

--- a/MAC286_3076_Data Structures_Spring2026_Attndance.xlsx
+++ b/MAC286_3076_Data Structures_Spring2026_Attndance.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="17280" windowHeight="6912"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="17256" windowHeight="5424"/>
   </bookViews>
   <sheets>
     <sheet name="Grades" sheetId="1" r:id="rId1"/>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="226" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="254" uniqueCount="36">
   <si>
     <t>Last Name</t>
   </si>
@@ -129,6 +129,9 @@
   </si>
   <si>
     <t>Late</t>
+  </si>
+  <si>
+    <t>ex</t>
   </si>
 </sst>
 </file>
@@ -937,14 +940,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:P15"/>
+  <dimension ref="A1:R15"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="3" max="14" width="3.5546875" customWidth="1"/>
     <col min="16" max="16" width="9.5546875" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="9.6640625" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="9.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -993,8 +998,14 @@
       <c r="P1" s="1">
         <v>46154</v>
       </c>
+      <c r="Q1" s="1">
+        <v>46156</v>
+      </c>
+      <c r="R1" s="1">
+        <v>46161</v>
+      </c>
     </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -1041,10 +1052,16 @@
         <v>30</v>
       </c>
       <c r="P2" t="s">
-        <v>31</v>
+        <v>35</v>
+      </c>
+      <c r="Q2" t="s">
+        <v>30</v>
+      </c>
+      <c r="R2" t="s">
+        <v>30</v>
       </c>
     </row>
-    <row r="3" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:18" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
         <v>4</v>
       </c>
@@ -1093,8 +1110,14 @@
       <c r="P3" s="2" t="s">
         <v>30</v>
       </c>
+      <c r="Q3" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="R3" s="2" t="s">
+        <v>30</v>
+      </c>
     </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>6</v>
       </c>
@@ -1143,8 +1166,14 @@
       <c r="P4" t="s">
         <v>30</v>
       </c>
+      <c r="Q4" t="s">
+        <v>30</v>
+      </c>
+      <c r="R4" t="s">
+        <v>34</v>
+      </c>
     </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>8</v>
       </c>
@@ -1193,8 +1222,14 @@
       <c r="P5" t="s">
         <v>30</v>
       </c>
+      <c r="Q5" t="s">
+        <v>30</v>
+      </c>
+      <c r="R5" t="s">
+        <v>30</v>
+      </c>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>10</v>
       </c>
@@ -1243,8 +1278,14 @@
       <c r="P6" t="s">
         <v>30</v>
       </c>
+      <c r="Q6" t="s">
+        <v>30</v>
+      </c>
+      <c r="R6" t="s">
+        <v>30</v>
+      </c>
     </row>
-    <row r="7" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:18" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
         <v>12</v>
       </c>
@@ -1293,8 +1334,14 @@
       <c r="P7" s="2" t="s">
         <v>34</v>
       </c>
+      <c r="Q7" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="R7" s="2" t="s">
+        <v>30</v>
+      </c>
     </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>14</v>
       </c>
@@ -1343,8 +1390,14 @@
       <c r="P8" t="s">
         <v>32</v>
       </c>
+      <c r="Q8" t="s">
+        <v>30</v>
+      </c>
+      <c r="R8" t="s">
+        <v>30</v>
+      </c>
     </row>
-    <row r="9" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:18" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
         <v>16</v>
       </c>
@@ -1385,7 +1438,7 @@
         <v>33</v>
       </c>
       <c r="N9" s="2" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="O9" s="2" t="s">
         <v>30</v>
@@ -1393,8 +1446,14 @@
       <c r="P9" s="2" t="s">
         <v>30</v>
       </c>
+      <c r="Q9" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="R9" s="2" t="s">
+        <v>31</v>
+      </c>
     </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>18</v>
       </c>
@@ -1443,8 +1502,14 @@
       <c r="P10" t="s">
         <v>30</v>
       </c>
+      <c r="Q10" t="s">
+        <v>30</v>
+      </c>
+      <c r="R10" t="s">
+        <v>32</v>
+      </c>
     </row>
-    <row r="11" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:18" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A11" s="2" t="s">
         <v>20</v>
       </c>
@@ -1493,8 +1558,14 @@
       <c r="P11" s="2" t="s">
         <v>30</v>
       </c>
+      <c r="Q11" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="R11" s="2" t="s">
+        <v>30</v>
+      </c>
     </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>22</v>
       </c>
@@ -1543,8 +1614,14 @@
       <c r="P12" t="s">
         <v>30</v>
       </c>
+      <c r="Q12" t="s">
+        <v>30</v>
+      </c>
+      <c r="R12" t="s">
+        <v>30</v>
+      </c>
     </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>24</v>
       </c>
@@ -1593,8 +1670,14 @@
       <c r="P13" s="2" t="s">
         <v>30</v>
       </c>
+      <c r="Q13" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="R13" s="2" t="s">
+        <v>30</v>
+      </c>
     </row>
-    <row r="14" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:18" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A14" s="2" t="s">
         <v>26</v>
       </c>
@@ -1643,8 +1726,14 @@
       <c r="P14" s="2" t="s">
         <v>30</v>
       </c>
+      <c r="Q14" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="R14" s="2" t="s">
+        <v>30</v>
+      </c>
     </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>28</v>
       </c>
@@ -1691,6 +1780,12 @@
         <v>30</v>
       </c>
       <c r="P15" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="Q15" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="R15" s="2" t="s">
         <v>30</v>
       </c>
     </row>
